--- a/results/04_final_refined_daily_hydroclimate_data/601/Wet_bulb_temp_15h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Wet_bulb_temp_15h00_timeseries.xlsx
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>16</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="26" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/601/Wet_bulb_temp_15h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Wet_bulb_temp_15h00_timeseries.xlsx
@@ -568,7 +568,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>15</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -596,7 +596,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>16.6</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -610,7 +610,7 @@
         <v>15</v>
       </c>
       <c r="D16">
-        <v>15.7</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -638,7 +638,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>15.7</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -680,7 +680,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>16</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -708,7 +708,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>13.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -722,7 +722,7 @@
         <v>23</v>
       </c>
       <c r="D24">
-        <v>14.8</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -792,7 +792,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>15.7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -806,7 +806,7 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>14</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="31" spans="1:4">
